--- a/Result/profitability/4402.xlsx
+++ b/Result/profitability/4402.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.04500000000000011</v>
       </c>
       <c r="N2" t="n">
-        <v>9.326250000000002</v>
+        <v>6.16375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1112500000000001</v>
+        <v>-0.1437500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9662499999999996</v>
+        <v>3.277500000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1975000000000001</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.14625</v>
+        <v>-4.47875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4112500000000001</v>
+        <v>-0.4125000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.0975</v>
+        <v>-18.61125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4325000000000001</v>
+        <v>-0.4350000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.3225</v>
+        <v>-23.01625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4700000000000001</v>
+        <v>-0.4737500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-24.38125</v>
+        <v>-24.505</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5550000000000002</v>
+        <v>-0.555</v>
       </c>
       <c r="N8" t="n">
-        <v>-28.38375</v>
+        <v>-27.775</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.655</v>
+        <v>-0.6550000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>-33.55875</v>
@@ -1772,7 +1772,7 @@
         <v>3.83</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.10375</v>
+        <v>-0.1037500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-33.8375</v>
@@ -1899,7 +1899,7 @@
         <v>-0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.08750000000000006</v>
+        <v>-0.08750000000000009</v>
       </c>
       <c r="N12" t="n">
         <v>-29.95125</v>
@@ -2026,7 +2026,7 @@
         <v>-0.72</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03999999999999995</v>
+        <v>0.0399999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-18.595</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4402</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-103.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.007500000000000114</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.02375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5305010893246189</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2263215859030837</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
